--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0082.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0082.xlsx
@@ -7210,7 +7210,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Tốt nhất là r?i ?i. Nơi này... chẳng dẫn đến "cứu rỗi" gì đâu.</t>
+          <t>Tốt nhất là Rời đi. Nơi này... chẳng dẫn đến "cứu rỗi" gì đâu.</t>
         </is>
       </c>
     </row>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Dù sao, ưu tiên của chúng ta bây giờ là tập trung lực lượng, giữ vững phòng tuyến và tận dụng thời gian mà cô ấy đang爭取 cho chúng ta.</t>
+          <t>Dù sao, ưu tiên của chúng ta bây giờ là tập trung lực lượng, giữ vững phòng tuyến và tận dụng thời gian mà cô ấy đang kéo dài cho chúng ta.</t>
         </is>
       </c>
     </row>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Kiếm không phân biệt đối xử. R?i ?i. Kẻ này là của ta.</t>
+          <t>Kiếm không phân biệt đối xử. Rời đi. Kẻ này là của ta.</t>
         </is>
       </c>
     </row>
